--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_11_Guardrails _ AI Safety/Day_11_Phan_01_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_11_Guardrails _ AI Safety/Day_11_Phan_01_22_Cau.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>60</v>
@@ -687,7 +687,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đếm công cụ không cho biết chúng chạm vào dữ liệu hay thực hiện hành động nào.</t>
+          <t>Đếm số lượng công cụ không phản ánh đúng mức độ rủi ro; phải phân tích chi tiết dữ liệu truy cập, quyền hạn, quyền tự chủ, tính khả nghịch và hậu quả của từng công cụ.</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>60</v>
@@ -1191,7 +1191,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách hình thức của prompt khỏi mục tiêu cuối theo policy.</t>
+          <t>Bản chất của kỹ thuật jailbreak là cố tình vượt qua các chính sách và bộ lọc an toàn của hệ thống để đạt được mục tiêu bị cấm, không phụ thuộc vào việc có dùng nhập vai hay không.</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1237,7 +1237,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm mục tiêu cuối mà người dùng muốn đạt.</t>
+          <t>Một prompt sử dụng kỹ thuật nhập vai nhưng chỉ phân tích nhân vật hư cấu và không yêu cầu nội dung vi phạm chính sách thì không phải là jailbreak; cần đánh giá theo mục tiêu cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1285,7 +1285,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đọc lịch sử như một chuỗi mục tiêu, không đặt lại ở mỗi lượt.</t>
+          <t>Khi kẻ tấn công thăm dò từng bước nhỏ (multi-turn reconnaissance), hệ thống cần phát hiện ý định tích lũy qua toàn bộ lịch sử hội thoại và chặn tại lượt 4 khi yêu cầu xâu chuỗi dữ liệu nhạy cảm xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o3 → o4 → o1</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1385,7 +1385,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định lần đầu bí mật đi khỏi ranh giới được bảo vệ.</t>
+          <t>Chuỗi rò rỉ bí mật đi từ nguồn dữ liệu lưu trữ được bảo vệ trong database (o2) → được công cụ truy xuất đưa vào context (o3) → mô hình tạo output chứa bí mật đó (o4) → gửi ra bên ngoài qua kênh HTTP sink (o1).</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1433,7 +1433,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đếm tập thông tin đã phát hành, không chỉ phản hồi hiện tại.</t>
+          <t>Chính sách giới hạn thông tin nhạy cảm áp dụng trên toàn bộ phiên làm việc (session scope); lượt 1 và 2 đã trả 2 thuộc tính, do đó yêu cầu thuộc tính thứ 3 ở lượt 3 phải bị chặn hoặc giữ lại để không vượt quá ngưỡng tích lũy.</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>60</v>
@@ -1481,7 +1481,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Khoanh vùng phiên bản, artifact và nơi chúng đã được dùng.</t>
+          <t>Khi phát hiện dependency độc hại chèn lệnh lạ ở môi trường staging, biện pháp cô lập chuẩn là phong tỏa artifact tại staging, đóng băng hoặc rollback dependency và chặn tuyệt đối đường deploy lên production.</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1529,7 +1529,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm representation trước nội dung.</t>
+          <t>Quy tắc kiểm tra ranh giới: Lỗi encoding (byte không thể giải mã) và định dạng dữ liệu phải bị từ chối ngay tại tầng kiểm tra dữ liệu đầu vào (input validation) trước khi gửi tới mô hình.</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>60</v>
@@ -1577,7 +1577,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So quyết định trước/sau khi chuẩn hóa trên cặp biểu diễn tương đương.</t>
+          <t>Nguyên lý bất biến an toàn (safety invariance): Sau khi chuẩn hóa an toàn (loại bỏ ký tự zero-width, homoglyphs), các biểu diễn có cùng ý định ngữ nghĩa phải nhận cùng một quyết định xử lý theo chính sách.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G23" s="3" t="n"/>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>60</v>
@@ -1625,7 +1625,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Rule phải nêu nó match cái gì, sau transform nào.</t>
+          <t>Khi phát hiện đầu vào khớp với chữ ký tấn công đã biết từ red-team, detector phải ghi nhận rõ quy tắc đã khớp, lý do kỹ thuật và áp dụng hành động tương ứng theo chính sách bảo mật.</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>60</v>
@@ -1673,7 +1673,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một layer cho qua không đồng nghĩa toàn bộ input an toàn.</t>
+          <t>Khi regex cho qua nhưng detector học máy (learned detector) cảnh báo tấn công với xác suất 0,91 vượt ngưỡng 0,85, hệ thống phải chặn hoặc chuyển duyệt theo kết quả learned detector, đồng thời lưu vết cả hai để kiểm toán.</t>
         </is>
       </c>
     </row>
